--- a/SponsorshipOverview.xlsx
+++ b/SponsorshipOverview.xlsx
@@ -9,464 +9,473 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </numFmts>
-  <fonts count="3">
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-  </fonts>
-  <fills count="3">
-    <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
-      <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F3864"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-  </fills>
-  <borders count="9">
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-  </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </cellStyleXfs>
-  <cellXfs count="108">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-  </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </cellStyles>
-</styleSheet>
+<ns0:styleSheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <ns0:numFmts count="1">
+    <ns0:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </ns0:numFmts>
+  <ns0:fonts count="4">
+    <ns0:font>
+      <ns0:sz val="11"/>
+      <ns0:name val="Calibri"/>
+    </ns0:font>
+    <ns0:font>
+      <ns0:b/>
+      <ns0:sz val="11"/>
+      <ns0:color rgb="FFFFFFFF"/>
+      <ns0:name val="Calibri"/>
+    </ns0:font>
+    <ns0:font>
+      <ns0:b/>
+      <ns0:sz val="11"/>
+      <ns0:color rgb="FF000000"/>
+      <ns0:name val="Calibri"/>
+    </ns0:font>
+    <ns0:font>
+      <ns0:i/>
+      <ns0:sz val="11"/>
+      <ns0:color rgb="FF808080"/>
+      <ns0:name val="Calibri"/>
+    </ns0:font>
+  </ns0:fonts>
+  <ns0:fills count="3">
+    <ns0:fill>
+      <ns0:patternFill patternType="none"/>
+    </ns0:fill>
+    <ns0:fill>
+      <ns0:patternFill patternType="gray125"/>
+    </ns0:fill>
+    <ns0:fill>
+      <ns0:patternFill patternType="solid">
+        <ns0:fgColor rgb="FF1F3864"/>
+        <ns0:bgColor indexed="64"/>
+      </ns0:patternFill>
+    </ns0:fill>
+  </ns0:fills>
+  <ns0:borders count="9">
+    <ns0:border>
+      <ns0:left style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:left>
+      <ns0:right/>
+      <ns0:top/>
+      <ns0:bottom/>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:left>
+      <ns0:right/>
+      <ns0:top style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:top>
+      <ns0:bottom/>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left/>
+      <ns0:right style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:right>
+      <ns0:top/>
+      <ns0:bottom/>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left/>
+      <ns0:right style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:right>
+      <ns0:top/>
+      <ns0:bottom style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:bottom>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:left>
+      <ns0:right/>
+      <ns0:top/>
+      <ns0:bottom style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:bottom>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left/>
+      <ns0:right style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:right>
+      <ns0:top style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:top>
+      <ns0:bottom/>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left/>
+      <ns0:right/>
+      <ns0:top/>
+      <ns0:bottom/>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left/>
+      <ns0:right/>
+      <ns0:top style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:top>
+      <ns0:bottom/>
+      <ns0:diagonal/>
+    </ns0:border>
+    <ns0:border>
+      <ns0:left/>
+      <ns0:right/>
+      <ns0:top/>
+      <ns0:bottom style="thin">
+        <ns0:color indexed="64"/>
+      </ns0:bottom>
+      <ns0:diagonal/>
+    </ns0:border>
+  </ns0:borders>
+  <ns0:cellStyleXfs count="1">
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </ns0:cellStyleXfs>
+  <ns0:cellXfs count="109">
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="center" vertical="center"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+    <ns0:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </ns0:xf>
+  </ns0:cellXfs>
+  <ns0:cellStyles count="1">
+    <ns0:cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </ns0:cellStyles>
+</ns0:styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -675,10 +684,14 @@
       <c r="C4" s="78">
         <v>72.2</v>
       </c>
-      <c r="D4" s="78">
+      <c r="D4" s="6">
         <v>2004</v>
       </c>
-      <c r="E4" s="78"/>
+      <c r="E4" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Longest-running global partner and official logistics provider since 2004.</t>
@@ -828,10 +841,14 @@
       <c r="C9" s="78">
         <v>44.3</v>
       </c>
-      <c r="D9" s="78">
+      <c r="D9" s="6">
         <v>2018</v>
       </c>
-      <c r="E9" s="78"/>
+      <c r="E9" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Global partner on a cash-plus-value-in-kind structure; largest revenue line after DHL.</t>
@@ -888,10 +905,14 @@
       <c r="C11" s="78">
         <v>30.8</v>
       </c>
-      <c r="D11" s="78">
+      <c r="D11" s="6">
         <v>2025</v>
       </c>
-      <c r="E11" s="78"/>
+      <c r="E11" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Global partner including Motorola and the Canada/Austria race titles.</t>
@@ -1041,10 +1062,14 @@
       <c r="C16" s="78">
         <v>14</v>
       </c>
-      <c r="D16" s="78">
+      <c r="D16" s="6">
         <v>2024</v>
       </c>
-      <c r="E16" s="78"/>
+      <c r="E16" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F16" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Expanded global partnership estimated in the high eight figures annually.</t>
@@ -1132,10 +1157,14 @@
       <c r="C19" s="78">
         <v>11.5</v>
       </c>
-      <c r="D19" s="78">
+      <c r="D19" s="6">
         <v>2025</v>
       </c>
-      <c r="E19" s="78"/>
+      <c r="E19" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official retail bank focused on the Openbank brand.</t>
@@ -1161,10 +1190,14 @@
       <c r="C20" s="78">
         <v>9.6</v>
       </c>
-      <c r="D20" s="78">
+      <c r="D20" s="6">
         <v>2025</v>
       </c>
-      <c r="E20" s="78"/>
+      <c r="E20" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F20" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official lottery partner, extended in Liberty's Q1 2026 quarter.</t>
@@ -1190,10 +1223,14 @@
       <c r="C21" s="78">
         <v>11.1</v>
       </c>
-      <c r="D21" s="78">
+      <c r="D21" s="6">
         <v>2026</v>
       </c>
-      <c r="E21" s="78"/>
+      <c r="E21" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">New for 2026 and also backs F1 Academy.</t>
@@ -1219,10 +1256,14 @@
       <c r="C22" s="78">
         <v>4.8</v>
       </c>
-      <c r="D22" s="78">
+      <c r="D22" s="6">
         <v>2025</v>
       </c>
-      <c r="E22" s="78"/>
+      <c r="E22" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official pasta partner supplying Paddock Club pasta bars.</t>
@@ -1248,8 +1289,14 @@
       <c r="C23" s="78">
         <v>5</v>
       </c>
-      <c r="D23" s="78"/>
-      <c r="E23" s="78"/>
+      <c r="D23" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E23" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Pit-wall CDS and streaming work, largely value-in-kind.</t>
@@ -1275,9 +1322,13 @@
       <c r="C24" s="78">
         <v>4.3</v>
       </c>
-      <c r="D24" s="78"/>
-      <c r="E24" s="78">
-        <v>2026</v>
+      <c r="D24" s="6">
+        <v>2025</v>
+      </c>
+      <c r="E24" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
@@ -1304,8 +1355,14 @@
       <c r="C25" s="78">
         <v>4</v>
       </c>
-      <c r="D25" s="78"/>
-      <c r="E25" s="78"/>
+      <c r="D25" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E25" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Promotional tie-in, not a media-rights fee.</t>
@@ -1331,10 +1388,14 @@
       <c r="C26" s="78">
         <v>2.9</v>
       </c>
-      <c r="D26" s="78">
+      <c r="D26" s="6">
         <v>2025</v>
       </c>
-      <c r="E26" s="78"/>
+      <c r="E26" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F26" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official consulting partner since April 2025.</t>
@@ -1360,10 +1421,14 @@
       <c r="C27" s="78">
         <v>7.4</v>
       </c>
-      <c r="D27" s="78">
+      <c r="D27" s="6">
         <v>2026</v>
       </c>
-      <c r="E27" s="78"/>
+      <c r="E27" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">New in 2026 with a dedicated content series.</t>
@@ -1389,8 +1454,14 @@
       <c r="C28" s="78">
         <v>7.5</v>
       </c>
-      <c r="D28" s="78"/>
-      <c r="E28" s="78"/>
+      <c r="D28" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E28" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">League-booked Las Vegas GP partner, part of the event sponsorship stack.</t>
@@ -1416,8 +1487,14 @@
       <c r="C29" s="78">
         <v>10</v>
       </c>
-      <c r="D29" s="78"/>
-      <c r="E29" s="78"/>
+      <c r="D29" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E29" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official apparel supplier with a partly in-kind fee.</t>
@@ -1443,10 +1520,14 @@
       <c r="C30" s="78">
         <v>3.7</v>
       </c>
-      <c r="D30" s="78">
+      <c r="D30" s="6">
         <v>2026</v>
       </c>
-      <c r="E30" s="78"/>
+      <c r="E30" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official private aviation supplier from July 2026.</t>
@@ -1472,8 +1553,14 @@
       <c r="C31" s="78">
         <v>3</v>
       </c>
-      <c r="D31" s="78"/>
-      <c r="E31" s="78"/>
+      <c r="D31" s="6">
+        <v>2024</v>
+      </c>
+      <c r="E31" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Official provider of mobile power.</t>
@@ -1499,8 +1586,14 @@
       <c r="C32" s="78">
         <v>3</v>
       </c>
-      <c r="D32" s="78"/>
-      <c r="E32" s="78"/>
+      <c r="D32" s="6">
+        <v>2022</v>
+      </c>
+      <c r="E32" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Longstanding broadcast connectivity supplier.</t>
@@ -1557,10 +1650,14 @@
       <c r="C34" s="78">
         <v>8</v>
       </c>
-      <c r="D34" s="78">
+      <c r="D34" s="6">
         <v>2024</v>
       </c>
-      <c r="E34" s="78"/>
+      <c r="E34" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America regional partner.</t>
@@ -1586,10 +1683,14 @@
       <c r="C35" s="78">
         <v>4.3</v>
       </c>
-      <c r="D35" s="78">
+      <c r="D35" s="6">
         <v>2022</v>
       </c>
-      <c r="E35" s="78"/>
+      <c r="E35" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional 5G partner centered on the Las Vegas GP.</t>
@@ -1615,10 +1716,14 @@
       <c r="C36" s="78">
         <v>7.4</v>
       </c>
-      <c r="D36" s="78">
+      <c r="D36" s="6">
         <v>2026</v>
       </c>
-      <c r="E36" s="78"/>
+      <c r="E36" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F36" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Non-exclusive official betting operator without on-track branding.</t>
@@ -1644,10 +1749,14 @@
       <c r="C37" s="78">
         <v>3.7</v>
       </c>
-      <c r="D37" s="78">
+      <c r="D37" s="6">
         <v>2026</v>
       </c>
-      <c r="E37" s="78"/>
+      <c r="E37" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">US and Canada betting operator rights.</t>
@@ -1673,8 +1782,16 @@
       <c r="C38" s="78">
         <v>22.2</v>
       </c>
-      <c r="D38" s="78"/>
-      <c r="E38" s="78"/>
+      <c r="D38" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
+      <c r="E38" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">n/a</t>
+        </is>
+      </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">Filed digital advertising revenue from F1's own media company, not a partner fee.</t>
@@ -1700,10 +1817,14 @@
       <c r="C39" s="78">
         <v>1.9</v>
       </c>
-      <c r="D39" s="78">
+      <c r="D39" s="6">
         <v>2026</v>
       </c>
-      <c r="E39" s="78"/>
+      <c r="E39" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">New multi-year deal covering global licensing and F1 Sim Racing sponsorship.</t>
@@ -1729,10 +1850,14 @@
       <c r="C40" s="80">
         <v>1.4</v>
       </c>
-      <c r="D40" s="80">
+      <c r="D40" s="6">
         <v>2025</v>
       </c>
-      <c r="E40" s="80"/>
+      <c r="E40" s="108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
       <c r="F40" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">Official betting data supplier behind the Betway and FanDuel odds.</t>

--- a/SponsorshipOverview.xlsx
+++ b/SponsorshipOverview.xlsx
@@ -4,478 +4,251 @@
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
     <sheet name="Sponsorship" sheetId="2" r:id="rId2"/>
+    <sheet name="2027 vs 2026" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<ns0:styleSheet xmlns:ns0="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <ns0:numFmts count="1">
-    <ns0:numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-  </ns0:numFmts>
-  <ns0:fonts count="4">
-    <ns0:font>
-      <ns0:sz val="11"/>
-      <ns0:name val="Calibri"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:b/>
-      <ns0:sz val="11"/>
-      <ns0:color rgb="FFFFFFFF"/>
-      <ns0:name val="Calibri"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:b/>
-      <ns0:sz val="11"/>
-      <ns0:color rgb="FF000000"/>
-      <ns0:name val="Calibri"/>
-    </ns0:font>
-    <ns0:font>
-      <ns0:i/>
-      <ns0:sz val="11"/>
-      <ns0:color rgb="FF808080"/>
-      <ns0:name val="Calibri"/>
-    </ns0:font>
-  </ns0:fonts>
-  <ns0:fills count="3">
-    <ns0:fill>
-      <ns0:patternFill patternType="none"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="gray125"/>
-    </ns0:fill>
-    <ns0:fill>
-      <ns0:patternFill patternType="solid">
-        <ns0:fgColor rgb="FF1F3864"/>
-        <ns0:bgColor indexed="64"/>
-      </ns0:patternFill>
-    </ns0:fill>
-  </ns0:fills>
-  <ns0:borders count="9">
-    <ns0:border>
-      <ns0:left style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:left>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:left>
-      <ns0:right/>
-      <ns0:top style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:top>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:right>
-      <ns0:top/>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:right>
-      <ns0:top/>
-      <ns0:bottom style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:bottom>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:left>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:bottom>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:right>
-      <ns0:top style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:top>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right/>
-      <ns0:top style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:top>
-      <ns0:bottom/>
-      <ns0:diagonal/>
-    </ns0:border>
-    <ns0:border>
-      <ns0:left/>
-      <ns0:right/>
-      <ns0:top/>
-      <ns0:bottom style="thin">
-        <ns0:color indexed="64"/>
-      </ns0:bottom>
-      <ns0:diagonal/>
-    </ns0:border>
-  </ns0:borders>
-  <ns0:cellStyleXfs count="1">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-  </ns0:cellStyleXfs>
-  <ns0:cellXfs count="109">
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="164" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="center" vertical="center"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="3" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-    <ns0:xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <ns0:alignment horizontal="left" vertical="center" wrapText="1"/>
-    </ns0:xf>
-  </ns0:cellXfs>
-  <ns0:cellStyles count="1">
-    <ns0:cellStyle name="Normal" xfId="0" builtinId="0"/>
-  </ns0:cellStyles>
-</ns0:styleSheet>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="3">
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+  </fonts>
+  <fills count="3">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F3864"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="9">
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="36">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+</styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -486,70 +259,70 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="19" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Field</t>
         </is>
       </c>
-      <c r="B1" s="59" t="inlineStr">
+      <c r="B1" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Value</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Title</t>
         </is>
       </c>
-      <c r="B2" s="38" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula 1 Sponsorship Overview</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
-      <c r="B3" s="38" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Sponsorship agreements (1).xlsx (FY2026 revenue column)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="0" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Table</t>
         </is>
       </c>
-      <c r="B4" s="38" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Partner | Tier | Estimated Annual Rev ($M) | Start Date | End Date | Notes | Source</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="0" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Rows</t>
         </is>
       </c>
-      <c r="B5" s="38">
+      <c r="B5" s="2">
         <v>39</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Created</t>
         </is>
       </c>
-      <c r="B6" s="39" t="inlineStr">
+      <c r="B6" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">2026-10-26</t>
         </is>
@@ -572,1300 +345,1455 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="28" t="inlineStr">
+      <c r="A1" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">Partner</t>
         </is>
       </c>
-      <c r="B1" s="34" t="inlineStr">
+      <c r="B1" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Tier</t>
         </is>
       </c>
-      <c r="C1" s="97" t="inlineStr">
+      <c r="C1" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Estimated Annual Rev ($M)</t>
         </is>
       </c>
-      <c r="D1" s="97" t="inlineStr">
+      <c r="D1" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Start Date</t>
         </is>
       </c>
-      <c r="E1" s="97" t="inlineStr">
+      <c r="E1" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">End Date</t>
         </is>
       </c>
-      <c r="F1" s="34" t="inlineStr">
+      <c r="F1" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">Notes</t>
         </is>
       </c>
-      <c r="G1" s="32" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">Source</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">LVMH (Louis Vuitton / Moët Hennessy / TAG Heuer)</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C2" s="78">
+      <c r="C2" s="6">
         <v>112.7</v>
       </c>
-      <c r="D2" s="78">
+      <c r="D2" s="6">
         <v>2025</v>
       </c>
-      <c r="E2" s="78">
+      <c r="E2" s="6">
         <v>2034</v>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Ten-year deal from 2025 covering Louis Vuitton, Moët Hennessy and TAG Heuer.</t>
         </is>
       </c>
-      <c r="G2" s="11" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Reuters &gt;$100M/yr; BlackBook/SportsPro ~$150; Ampere $1bn/10yr=$100 (trade press)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="9" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Aramco</t>
         </is>
       </c>
-      <c r="B3" s="15" t="inlineStr">
+      <c r="B3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C3" s="78">
+      <c r="C3" s="6">
         <v>47.6</v>
       </c>
-      <c r="D3" s="78">
+      <c r="D3" s="6">
         <v>2020</v>
       </c>
-      <c r="E3" s="78">
+      <c r="E3" s="6">
         <v>2029</v>
       </c>
-      <c r="F3" s="15" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global partner through 2029 and 2027 Hungarian GP title holder.</t>
         </is>
       </c>
-      <c r="G3" s="11" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SportBusiness ~$40–45; MotorsportWeek ~$42–51 / ~$450M total (trade press)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="9" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DHL</t>
         </is>
       </c>
-      <c r="B4" s="15" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C4" s="78">
+      <c r="C4" s="6">
         <v>72.2</v>
       </c>
       <c r="D4" s="6">
         <v>2004</v>
       </c>
-      <c r="E4" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F4" s="15" t="inlineStr">
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Longest-running global partner and official logistics provider since 2004.</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BlackBook portfolio 2025 $40M/yr extension 2024 (trade press)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Heineken</t>
         </is>
       </c>
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C5" s="78">
+      <c r="C5" s="6">
         <v>59.6</v>
       </c>
-      <c r="D5" s="78">
+      <c r="D5" s="6">
         <v>2016</v>
       </c>
-      <c r="E5" s="78">
+      <c r="E5" s="6">
         <v>2027</v>
       </c>
-      <c r="F5" s="15" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Renewed Nov 2025 and expanded with race titles in Brazil, Madrid and Silverstone from 2027.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BlackBook/Luscid $250M/5yr; drinks-intel ~$50/yr; Heineken Co PR 5 Nov 2025 multi-yr renewal (trade press)</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">MSC Cruises</t>
         </is>
       </c>
-      <c r="B6" s="15" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C6" s="78">
+      <c r="C6" s="6">
         <v>35</v>
       </c>
-      <c r="D6" s="78">
+      <c r="D6" s="6">
         <v>2022</v>
       </c>
-      <c r="E6" s="78">
+      <c r="E6" s="6">
         <v>2030</v>
       </c>
-      <c r="F6" s="15" t="inlineStr">
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Extended through 2030 and holds titles in Barcelona, the US, São Paulo, Spa and Türkiye.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GlobalData via Sportcal ~$35/yr thru 2026; MSC PR ext thru 2030; Explora Journeys noted (trade press)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Salesforce</t>
         </is>
       </c>
-      <c r="B7" s="15" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C7" s="78">
+      <c r="C7" s="6">
         <v>31.8</v>
       </c>
-      <c r="D7" s="78">
+      <c r="D7" s="6">
         <v>2022</v>
       </c>
-      <c r="E7" s="78">
+      <c r="E7" s="6">
         <v>2027</v>
       </c>
-      <c r="F7" s="15" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Renewed early with an Agentforce focus and also backs the Las Vegas GP and F1 Academy.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">BlackBook/FOS ~$30×5; SportsPro Agentforce; Liberty Q1'26 ext (trade press)</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Crypto.com</t>
         </is>
       </c>
-      <c r="B8" s="15" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner (exclusive crypto)</t>
         </is>
       </c>
-      <c r="C8" s="78">
+      <c r="C8" s="6">
         <v>20</v>
       </c>
-      <c r="D8" s="78">
+      <c r="D8" s="6">
         <v>2021</v>
       </c>
-      <c r="E8" s="78">
+      <c r="E8" s="6">
         <v>2030</v>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Crypto category exclusive through 2030; the Miami GP title is a separate promoter deal.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">FWON prior ~$100M/5yr; BlackBook/Sportcal ext ~$20/yr thru 2030 (trade press)</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">AWS</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C9" s="78">
+      <c r="C9" s="6">
         <v>44.3</v>
       </c>
       <c r="D9" s="6">
         <v>2018</v>
       </c>
-      <c r="E9" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F9" s="15" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global partner on a cash-plus-value-in-kind structure; largest revenue line after DHL.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SportsPro Global $40–50; Insights hybrid; Global since 2022; Otter Mar 2026 catalog-price color (estimate)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Qatar Airways</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C10" s="78">
+      <c r="C10" s="6">
         <v>49.9</v>
       </c>
-      <c r="D10" s="78">
+      <c r="D10" s="6">
         <v>2023</v>
       </c>
-      <c r="E10" s="78">
+      <c r="E10" s="6">
         <v>2027</v>
       </c>
-      <c r="F10" s="15" t="inlineStr">
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official airline through 2027 holding the Australia, Azerbaijan and Qatar race titles.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GP247 ~$46; SportBusiness Emirates~$25→asked ~2×; band 45–50 (trade press)</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Lenovo (+ Motorola)</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner</t>
         </is>
       </c>
-      <c r="C11" s="78">
+      <c r="C11" s="6">
         <v>30.8</v>
       </c>
       <c r="D11" s="6">
         <v>2025</v>
       </c>
-      <c r="E11" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F11" s="15" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global partner including Motorola and the Canada/Austria race titles.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SportsPro Global band; Jiemian; ASN soft Japan/Pan-Asia; prior Official SBJ; Otter Mar 2026 catalog-price color (estimate)</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Pirelli</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Global Partner (Tyre Supplier)</t>
         </is>
       </c>
-      <c r="C12" s="78">
+      <c r="C12" s="6">
         <v>41.3</v>
       </c>
-      <c r="D12" s="78">
+      <c r="D12" s="6">
         <v>2011</v>
       </c>
-      <c r="E12" s="78">
+      <c r="E12" s="6">
         <v>2028</v>
       </c>
-      <c r="F12" s="15" t="inlineStr">
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Sole tyre supplier whose option through 2028 was exercised in 2026.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">MilanoFinanza hist ~$43; AMuS bid soft; FIA option thru 2028; SportsPro Global low (estimate)</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Louis Vuitton</t>
         </is>
       </c>
-      <c r="B13" s="15" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner (LVMH maison)</t>
         </is>
       </c>
-      <c r="C13" s="78">
+      <c r="C13" s="6">
         <v>0</v>
       </c>
-      <c r="D13" s="78">
+      <c r="D13" s="6">
         <v>2025</v>
       </c>
-      <c r="E13" s="78">
+      <c r="E13" s="6">
         <v>2034</v>
       </c>
-      <c r="F13" s="15" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Roll-up inside the LVMH global deal; no separate revenue.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com partners; LVMH Global package (trade press)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Moët Hennessy</t>
         </is>
       </c>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner (LVMH maison)</t>
         </is>
       </c>
-      <c r="C14" s="78">
+      <c r="C14" s="6">
         <v>0</v>
       </c>
-      <c r="D14" s="78">
+      <c r="D14" s="6">
         <v>2025</v>
       </c>
-      <c r="E14" s="78">
+      <c r="E14" s="6">
         <v>2034</v>
       </c>
-      <c r="F14" s="15" t="inlineStr">
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Roll-up inside the LVMH global deal; no separate revenue.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com partners; LVMH Global package (trade press)</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">TAG Heuer</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner (LVMH maison)</t>
         </is>
       </c>
-      <c r="C15" s="78">
+      <c r="C15" s="6">
         <v>0</v>
       </c>
-      <c r="D15" s="78">
+      <c r="D15" s="6">
         <v>2025</v>
       </c>
-      <c r="E15" s="78">
+      <c r="E15" s="6">
         <v>2034</v>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Roll-up inside the LVMH global deal; no separate revenue.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com partners; LVMH Global package (trade press)</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">American Express</t>
         </is>
       </c>
-      <c r="B16" s="15" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C16" s="78">
+      <c r="C16" s="6">
         <v>14</v>
       </c>
       <c r="D16" s="6">
         <v>2024</v>
       </c>
-      <c r="E16" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F16" s="15" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Expanded global partnership estimated in the high eight figures annually.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SBJ 23 Oct 2024 eight figures; SportsPro Official ~half Global; Otter Maryanne 7/8/26 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PepsiCo (Sting / Gatorade / Doritos)</t>
         </is>
       </c>
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C17" s="78">
+      <c r="C17" s="6">
         <v>13.2</v>
       </c>
-      <c r="D17" s="78">
+      <c r="D17" s="6">
         <v>2025</v>
       </c>
-      <c r="E17" s="78">
+      <c r="E17" s="6">
         <v>2030</v>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Multi-brand deal through 2030 covering Sting, Gatorade and Doritos.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">SBJ 27 May 2025 eight figures; SportsPro Official ~half Global; Otter Maryanne 7/8/26 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Nestlé / KitKat</t>
         </is>
       </c>
-      <c r="B18" s="15" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C18" s="78">
+      <c r="C18" s="6">
         <v>9.8</v>
       </c>
-      <c r="D18" s="78">
+      <c r="D18" s="6">
         <v>2025</v>
       </c>
-      <c r="E18" s="78">
+      <c r="E18" s="6">
         <v>2028</v>
       </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">KitKat category deal through 2028, expanding worldwide in 2026.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Reuters ND; BlackBook; expands worldwide 2026; Otter Mar 2026 sponsorship strategy catalog-price color (estimate)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Santander</t>
         </is>
       </c>
-      <c r="B19" s="15" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C19" s="78">
+      <c r="C19" s="6">
         <v>11.5</v>
       </c>
       <c r="D19" s="6">
         <v>2025</v>
       </c>
-      <c r="E19" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F19" s="15" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official retail bank focused on the Openbank brand.</t>
         </is>
       </c>
-      <c r="G19" s="11" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Santander/F1 PR; Official retail bank / Openbank focus; SportsPro Official ~half Global; Otter Mar 2026 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Allwyn</t>
         </is>
       </c>
-      <c r="B20" s="15" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C20" s="78">
+      <c r="C20" s="6">
         <v>9.6</v>
       </c>
       <c r="D20" s="6">
         <v>2025</v>
       </c>
-      <c r="E20" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official lottery partner, extended in Liberty's Q1 2026 quarter.</t>
         </is>
       </c>
-      <c r="G20" s="11" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Official lottery Feb 2025; Liberty Q1'26 ext; Sportcal; Official Med PROXY; Otter Mar 2026 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Standard Chartered</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C21" s="78">
+      <c r="C21" s="6">
         <v>11.1</v>
       </c>
       <c r="D21" s="6">
         <v>2026</v>
       </c>
-      <c r="E21" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">New for 2026 and also backs F1 Academy.</t>
         </is>
       </c>
-      <c r="G21" s="11" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corp/SportsPro Jan 2026; Liberty Q1'26 new-sponsor cite; Otter Mar 2026 sponsorship strategy catalog-price color (estimate)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Barilla</t>
         </is>
       </c>
-      <c r="B22" s="15" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C22" s="78">
+      <c r="C22" s="6">
         <v>4.8</v>
       </c>
       <c r="D22" s="6">
         <v>2025</v>
       </c>
-      <c r="E22" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official pasta partner supplying Paddock Club pasta bars.</t>
         </is>
       </c>
-      <c r="G22" s="11" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com/ANSA Apr 2025 Official Pasta; Paddock Club pasta bars; ND fee; Otter Mar 2026 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Globant</t>
         </is>
       </c>
-      <c r="B23" s="15" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C23" s="78">
+      <c r="C23" s="6">
         <v>5</v>
       </c>
       <c r="D23" s="6">
         <v>2024</v>
       </c>
-      <c r="E23" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Pit-wall CDS and streaming work, largely value-in-kind.</t>
         </is>
       </c>
-      <c r="G23" s="11" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Partner; pit-wall CDS / streaming; VIK-heavy hybrid (estimate)</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">LIQUI MOLY</t>
         </is>
       </c>
-      <c r="B24" s="15" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C24" s="78">
+      <c r="C24" s="6">
         <v>4.3</v>
       </c>
       <c r="D24" s="6">
         <v>2025</v>
       </c>
-      <c r="E24" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F24" s="15" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Extended Sep 2026, moving to a new Official Supporter tier from 2027.</t>
         </is>
       </c>
-      <c r="G24" s="11" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com; LIQUI MOLY PR 23 Sep 2026; Sportcal (estimate)</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Paramount+</t>
         </is>
       </c>
-      <c r="B25" s="15" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C25" s="78">
+      <c r="C25" s="6">
         <v>4</v>
       </c>
       <c r="D25" s="6">
         <v>2023</v>
       </c>
-      <c r="E25" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Promotional tie-in, not a media-rights fee.</t>
         </is>
       </c>
-      <c r="G25" s="11" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Partner; promo hybrid (estimate)</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PwC</t>
         </is>
       </c>
-      <c r="B26" s="15" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C26" s="78">
+      <c r="C26" s="6">
         <v>2.9</v>
       </c>
       <c r="D26" s="6">
         <v>2025</v>
       </c>
-      <c r="E26" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official consulting partner since April 2025.</t>
         </is>
       </c>
-      <c r="G26" s="11" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Consulting Partner from ~Apr 2025; ND (estimate)</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Marsh</t>
         </is>
       </c>
-      <c r="B27" s="15" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C27" s="78">
+      <c r="C27" s="6">
         <v>7.4</v>
       </c>
       <c r="D27" s="6">
         <v>2026</v>
       </c>
-      <c r="E27" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">New in 2026 with a dedicated content series.</t>
         </is>
       </c>
-      <c r="G27" s="11" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Partner; announce ~28 Apr 2026; The Risk Perspective content series; Otter Mar 2026 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">LVCVA (Las Vegas Convention and Visitors Authority)</t>
         </is>
       </c>
-      <c r="B28" s="15" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Partner</t>
         </is>
       </c>
-      <c r="C28" s="78">
+      <c r="C28" s="6">
         <v>7.5</v>
       </c>
       <c r="D28" s="6">
         <v>2023</v>
       </c>
-      <c r="E28" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">League-booked Las Vegas GP partner, part of the event sponsorship stack.</t>
         </is>
       </c>
-      <c r="G28" s="11" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Sportcal Steve Hill LVCVA Vegas sponsorship element (trade press)</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">PUMA</t>
         </is>
       </c>
-      <c r="B29" s="15" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Provider</t>
         </is>
       </c>
-      <c r="C29" s="78">
+      <c r="C29" s="6">
         <v>10</v>
       </c>
       <c r="D29" s="6">
         <v>2023</v>
       </c>
-      <c r="E29" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official apparel supplier with a partly in-kind fee.</t>
         </is>
       </c>
-      <c r="G29" s="11" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">GlobalData/Sportcal ~$10; hybrid apparel may partly CP (trade press)</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Flexjet</t>
         </is>
       </c>
-      <c r="B30" s="15" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Provider</t>
         </is>
       </c>
-      <c r="C30" s="78">
+      <c r="C30" s="6">
         <v>3.7</v>
       </c>
       <c r="D30" s="6">
         <v>2026</v>
       </c>
-      <c r="E30" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official private aviation supplier from July 2026.</t>
         </is>
       </c>
-      <c r="G30" s="11" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corp/F1 Official Private Aviation Supplier PR 1 Jul 2026 (British GP); Otter Maryanne 7/8/26 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Aggreko</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Provider</t>
         </is>
       </c>
-      <c r="C31" s="78">
+      <c r="C31" s="6">
         <v>3</v>
       </c>
       <c r="D31" s="6">
         <v>2024</v>
       </c>
-      <c r="E31" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official provider of mobile power.</t>
         </is>
       </c>
-      <c r="G31" s="11" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Provider; Provider Low basket (estimate)</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Tata Communications</t>
         </is>
       </c>
-      <c r="B32" s="15" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Provider</t>
         </is>
       </c>
-      <c r="C32" s="78">
+      <c r="C32" s="6">
         <v>3</v>
       </c>
       <c r="D32" s="6">
         <v>2022</v>
       </c>
-      <c r="E32" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Longstanding broadcast connectivity supplier.</t>
         </is>
       </c>
-      <c r="G32" s="11" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Provider; longstanding broadcast contribution (estimate)</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="9" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fever</t>
         </is>
       </c>
-      <c r="B33" s="15" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Provider</t>
         </is>
       </c>
-      <c r="C33" s="78">
+      <c r="C33" s="6">
         <v>4</v>
       </c>
-      <c r="D33" s="78">
+      <c r="D33" s="6">
         <v>2027</v>
       </c>
-      <c r="E33" s="78">
+      <c r="E33" s="6">
         <v>2031</v>
       </c>
-      <c r="F33" s="15" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Five-year ticketing deal starting 2027, replacing Platinium.</t>
         </is>
       </c>
-      <c r="G33" s="11" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corp/Fever/SportBusiness Jun 2026; 5yr 2027–2031 Official Supplier ticketing on F1.com (estimate)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Arcos Dorados (McDonald's LatAm)</t>
         </is>
       </c>
-      <c r="B34" s="15" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional Partner</t>
         </is>
       </c>
-      <c r="C34" s="78">
+      <c r="C34" s="6">
         <v>8</v>
       </c>
       <c r="D34" s="6">
         <v>2024</v>
       </c>
-      <c r="E34" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F34" s="15" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Latin America regional partner.</t>
         </is>
       </c>
-      <c r="G34" s="11" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Regional Partner; soft Sportcal Pan Am; PROXY Regional mid (estimate)</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">T-Mobile</t>
         </is>
       </c>
-      <c r="B35" s="15" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional Partner</t>
         </is>
       </c>
-      <c r="C35" s="78">
+      <c r="C35" s="6">
         <v>4.3</v>
       </c>
       <c r="D35" s="6">
         <v>2022</v>
       </c>
-      <c r="E35" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F35" s="15" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Regional 5G partner centered on the Las Vegas GP.</t>
         </is>
       </c>
-      <c r="G35" s="11" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Exclusive 5G Partner of Heineken Las Vegas GP + Regional 5G Innovation Partner (estimate)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Betway</t>
         </is>
       </c>
-      <c r="B36" s="15" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Betting Operator</t>
         </is>
       </c>
-      <c r="C36" s="78">
+      <c r="C36" s="6">
         <v>7.4</v>
       </c>
       <c r="D36" s="6">
         <v>2026</v>
       </c>
-      <c r="E36" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Non-exclusive official betting operator without on-track branding.</t>
         </is>
       </c>
-      <c r="G36" s="11" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com Official Betting; SBJ 5 Mar 2026 non-exclusive; Super Group PR; Otter Mar 2026 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="9" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">FanDuel</t>
         </is>
       </c>
-      <c r="B37" s="15" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Betting Operator</t>
         </is>
       </c>
-      <c r="C37" s="78">
+      <c r="C37" s="6">
         <v>3.7</v>
       </c>
       <c r="D37" s="6">
         <v>2026</v>
       </c>
-      <c r="E37" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F37" s="15" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">US and Canada betting operator rights.</t>
         </is>
       </c>
-      <c r="G37" s="11" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com; announce ~30 Apr 2026 Official Betting Operator US+Canada; Otter Mar 2026 (estimate)</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Formula One Digital Media Ltd (digital advertising)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Digital advertising</t>
         </is>
       </c>
-      <c r="C38" s="78">
+      <c r="C38" s="6">
         <v>22.2</v>
       </c>
-      <c r="D38" s="108" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">n/a</t>
         </is>
       </c>
-      <c r="E38" s="108" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">n/a</t>
         </is>
       </c>
-      <c r="F38" s="15" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">Filed digital advertising revenue from F1's own media company, not a partner fee.</t>
         </is>
       </c>
-      <c r="G38" s="11" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Cos 08915039 YE25 Note 7 $22.155M (filed)</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">Fanatec (CORSAIR)</t>
         </is>
       </c>
-      <c r="B39" s="15" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">F1 Sim Racing Official Sponsor / Licensing</t>
         </is>
       </c>
-      <c r="C39" s="78">
+      <c r="C39" s="6">
         <v>1.9</v>
       </c>
       <c r="D39" s="6">
         <v>2026</v>
       </c>
-      <c r="E39" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F39" s="15" t="inlineStr">
+      <c r="E39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <t xml:space="preserve">New multi-year deal covering global licensing and F1 Sim Racing sponsorship.</t>
         </is>
       </c>
-      <c r="G39" s="11" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Corsair/Fanatec PR 23 Mar 2026; F1.com Sim Racing Official Sponsor (estimate)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="13" t="inlineStr">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">ALT Sports Data</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Official Betting Data Supplier</t>
         </is>
       </c>
-      <c r="C40" s="80">
+      <c r="C40" s="7">
         <v>1.4</v>
       </c>
-      <c r="D40" s="6">
+      <c r="D40" s="7">
         <v>2025</v>
       </c>
-      <c r="E40" s="108" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unannounced</t>
-        </is>
-      </c>
-      <c r="F40" s="17" t="inlineStr">
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Unannounced</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">Official betting data supplier behind the Betway and FanDuel odds.</t>
         </is>
       </c>
-      <c r="G40" s="12" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">F1.com PR 28 Feb 2025; BlackBook; Betway package refs ALT (estimate)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="26.00" customWidth="1"/>
+    <col min="2" max="2" width="100.00" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brand</t>
+        </is>
+      </c>
+      <c r="B1" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">What's changing in 2027</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fever</t>
+        </is>
+      </c>
+      <c r="B2" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New partner. Five-year Official Supplier ticketing deal (through 2031) from 2027, replacing Platinium. Confirmed by F1 release 16 Jun 2026 and listed on the official F1 2027 partner roster.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heineken</t>
+        </is>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adds three GP title partnerships from 2027: São Paulo (Brazil), Madrid and Silverstone. Keeps China and Las Vegas titles. Renewed Nov 2025 with naming rights of three GPs each season.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LIQUI MOLY</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Renewal announced 23 Sep 2026 moves it to the new Official Supporter tier; the release gives no start year, so 2027 is the first full season under the new tier.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MSC Cruises</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Increases race titles from three to five: adds Portuguese GP (Portimão) and Turkish GP (Istanbul, new five-year deal) to the existing US, São Paulo and Barcelona titles. Confirmed in MSC release 21 Sep 2026 and on the 2027 calendar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hard Rock</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes the Miami GP title from 2027 (becomes FORMULA 1 HARD ROCK MIAMI GRAND PRIX), replacing Crypto.com, which held the title since 2022. Multi-year deal announced 1 Sep 2026; Hard Rock was a founding partner since 2022.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aramco</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes the Hungarian GP title from 2027; AWS held it in 2026. Aramco already holds the Japanese title. Shown on the official 2027 calendar; no fee announced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lenovo (+ Motorola)</t>
+        </is>
+      </c>
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adds two titles from 2027: Japanese GP (from Aramco) and Spanish GP (Madrid, from MSC Cruises). Its 2026 Canada, Austria titles and the 2027 Canada title are not shown on any source; 2027 list only shows Lenovo on Japan and Spain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moët Hennessy (LVMH)</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes the Australian GP title from 2027, replacing Qatar Airways. Title sits inside the LVMH global fee, so no separate revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TAG Heuer (LVMH)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Takes the British GP title from 2027; Pirelli held it in 2026. Title sits inside the LVMH global fee, so no separate revenue.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pirelli</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adds the United States GP title from 2027, which MSC Cruises held in 2026; retains the Italian GP title.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Qatar Airways</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Adds the Austrian GP title from 2027 (Lenovo held it in 2026). Loses the Australian title to Moët and does not appear on the 2027 US GP card. Global deal was described as through 2027 in the notes; official 2027 calendar still shows Qatar title rounds.</t>
         </is>
       </c>
     </row>
